--- a/templates/INFRA GER ADV F - template.xlsx
+++ b/templates/INFRA GER ADV F - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$11</definedName>
@@ -1390,96 +1390,96 @@
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C19" s="32" t="n">
-        <v>1.01248189</v>
+        <v>1.01764752</v>
       </c>
       <c r="D19" s="33" t="n">
-        <v>0.0005101260056592505</v>
+        <v>0.0005085385965357681</v>
       </c>
       <c r="E19" s="33" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="34" t="n">
-        <v>0.9400430974994287</v>
+        <v>0.9371178731962512</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>1.01196566</v>
+        <v>1.01713027</v>
       </c>
       <c r="D20" s="37" t="n">
-        <v>0.0005101093953550073</v>
+        <v>0.0005087776564425273</v>
       </c>
       <c r="E20" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="38" t="n">
-        <v>0.9400124885877521</v>
+        <v>0.937558404776184</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
-        <v>1.01144971</v>
+        <v>1.01661304</v>
       </c>
       <c r="D21" s="37" t="n">
-        <v>0.0005101322143681308</v>
+        <v>0.0005087313983640485</v>
       </c>
       <c r="E21" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="38" t="n">
-        <v>0.9400545386999607</v>
+        <v>0.9374731619403058</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>1.010934</v>
+        <v>1.01609612</v>
       </c>
       <c r="D22" s="37" t="n">
-        <v>0.0005101153277498049</v>
+        <v>0.0005123300445684098</v>
       </c>
       <c r="E22" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F22" s="38" t="n">
-        <v>0.940023420605958</v>
+        <v>0.9441046264945988</v>
       </c>
     </row>
     <row r="23" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>1.01041857</v>
+        <v>1.01557581</v>
       </c>
       <c r="D23" s="37" t="n">
-        <v>0.0005101379104206494</v>
+        <v>0.0005083542861219481</v>
       </c>
       <c r="E23" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F23" s="38" t="n">
-        <v>0.9400650351945398</v>
+        <v>0.9367782321460272</v>
       </c>
     </row>
     <row r="24" ht="15.95" customHeight="1">
@@ -1519,18 +1519,18 @@
     <row r="26" ht="15.95" customFormat="1" customHeight="1" s="30">
       <c r="B26" s="51" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C26" s="51" t="inlineStr"/>
       <c r="D26" s="37" t="n">
-        <v>0.009856787478086604</v>
+        <v>0.003565370296159776</v>
       </c>
       <c r="E26" s="37" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F26" s="38" t="n">
-        <v>0.9402310383894398</v>
+        <v>0.9370652075226097</v>
       </c>
       <c r="G26" s="53" t="n"/>
     </row>
@@ -1542,13 +1542,13 @@
       </c>
       <c r="C27" s="51" t="inlineStr"/>
       <c r="D27" s="37" t="n">
-        <v>0.01090553445484788</v>
+        <v>0.01080561935592828</v>
       </c>
       <c r="E27" s="37" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F27" s="38" t="n">
-        <v>0.9403061510902889</v>
+        <v>0.9387684003134951</v>
       </c>
       <c r="G27" s="53" t="n"/>
     </row>
@@ -1560,13 +1560,13 @@
       </c>
       <c r="C28" s="39" t="inlineStr"/>
       <c r="D28" s="37" t="n">
-        <v>0.01248189000000011</v>
+        <v>0.01764751999999992</v>
       </c>
       <c r="E28" s="37" t="n">
-        <v>0.01327189162505582</v>
+        <v>0.01878398381837676</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>0.9404755819762511</v>
+        <v>0.9394982539718216</v>
       </c>
       <c r="G28" s="40" t="n"/>
     </row>
@@ -1578,13 +1578,13 @@
       </c>
       <c r="C29" s="39" t="inlineStr"/>
       <c r="D29" s="37" t="n">
-        <v>0.01248189000000011</v>
+        <v>0.01764751999999992</v>
       </c>
       <c r="E29" s="37" t="n">
-        <v>0.01327189162505582</v>
+        <v>0.01878398381837676</v>
       </c>
       <c r="F29" s="38" t="n">
-        <v>0.9404755819762511</v>
+        <v>0.9394982539718216</v>
       </c>
       <c r="G29" s="40" t="n"/>
     </row>
@@ -1612,7 +1612,7 @@
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="41" t="n">
-        <v>190420183.04</v>
+        <v>257726957.83</v>
       </c>
       <c r="F32" s="25" t="n"/>
       <c r="G32" s="3" t="n"/>
@@ -1627,7 +1627,7 @@
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="41" t="n">
-        <v>120291529.2416</v>
+        <v>150285364.734</v>
       </c>
       <c r="F33" s="25" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D35" s="17" t="n"/>
